--- a/OpenRefine_Templates/OpenRefineTemplate_Blank.xlsx
+++ b/OpenRefine_Templates/OpenRefineTemplate_Blank.xlsx
@@ -1,12 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arndts\Downloads\gits\GitHubDotCom\terminology-guide-for-move\OpenRefine_Templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12450"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Tabellenblatt1" sheetId="1" r:id="rId4"/>
+    <sheet name="Tabellenblatt1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -85,12 +93,6 @@
     <t>Begriff - redaktionelle Anmerkung (en)</t>
   </si>
   <si>
-    <t>Begriff - Anmerkung zur Bearbeitungshistorie (de)</t>
-  </si>
-  <si>
-    <t>Begriff - Anmerkung zur Bearbeitungshistorie (en)</t>
-  </si>
-  <si>
     <t>Begriff - Verfasser des Eintrags</t>
   </si>
   <si>
@@ -103,29 +105,44 @@
     <t>Begriff - Bearbeitungsstatus</t>
   </si>
   <si>
-    <t>Begriff - Mathematisches Symbol</t>
-  </si>
-  <si>
     <t>Begriff - Begriffsbeziehung - Oberbegriff</t>
+  </si>
+  <si>
+    <t>Begriff - Symbol oder Formelzeichen</t>
+  </si>
+  <si>
+    <t>Begriff - Anmerkung zur Änderungsvermerk (en)</t>
+  </si>
+  <si>
+    <t>Begriff - Änderungsvermerk (de)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd.MM.yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -134,11 +151,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="7">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF284E3F"/>
@@ -152,6 +175,7 @@
       <bottom style="thin">
         <color rgb="FF284E3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -166,6 +190,7 @@
       <bottom style="thin">
         <color rgb="FF284E3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -180,6 +205,7 @@
       <bottom style="thin">
         <color rgb="FF284E3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -194,6 +220,7 @@
       <bottom style="thin">
         <color rgb="FF284E3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -208,6 +235,7 @@
       <bottom style="thin">
         <color rgb="FF284E3F"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -222,144 +250,148 @@
       <bottom style="thin">
         <color rgb="FF284E3F"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF356854"/>
           <bgColor rgb="FF356854"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="3" pivot="0" name="Tabellenblatt1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Tabellenblatt1-style" pivot="0" count="3">
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:AF2" displayName="Tabelle1" name="Tabelle1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:AF2" headerRowDxfId="0">
   <tableColumns count="32">
-    <tableColumn name="Type" id="1"/>
-    <tableColumn name="Verfasser - ID" id="2"/>
-    <tableColumn name="Verfasser  - Nachname" id="3"/>
-    <tableColumn name="Verfasser - Vorname" id="4"/>
-    <tableColumn name="Verfasser - ORCiD" id="5"/>
-    <tableColumn name="Quellennachweis - ID" id="6"/>
-    <tableColumn name="Quellennachweis - Titel" id="7"/>
-    <tableColumn name="Quellennachweis - Verfasser" id="8"/>
-    <tableColumn name="Quellennachweis - Herausgeber" id="9"/>
-    <tableColumn name="Quellennachweis - Erscheinungsdatum" id="10"/>
-    <tableColumn name="Quellennachweis - Zugangslink" id="11"/>
-    <tableColumn name="Begriff - ID" id="12"/>
-    <tableColumn name="Begriff - bevorzugte Benennung (de)" id="13"/>
-    <tableColumn name="Begriff - bevorzugte Benennung (en)" id="14"/>
-    <tableColumn name="Begriff - alternative Benennung (de)" id="15"/>
-    <tableColumn name="Begriff - alternative Benennung (en)" id="16"/>
-    <tableColumn name="Begriff - Definition (de)" id="17"/>
-    <tableColumn name="Begriff - Definition (en)" id="18"/>
-    <tableColumn name="Begriff - Quellenangabe" id="19"/>
-    <tableColumn name="Begriff - Bearbeitungsdatum" id="20"/>
-    <tableColumn name="Begriff - Fachzuordnung" id="21"/>
-    <tableColumn name="Begriff - Erstellungsdatum" id="22"/>
-    <tableColumn name="Begriff - redaktionelle Anmerkung (de)" id="23"/>
-    <tableColumn name="Begriff - redaktionelle Anmerkung (en)" id="24"/>
-    <tableColumn name="Begriff - Anmerkung zur Bearbeitungshistorie (de)" id="25"/>
-    <tableColumn name="Begriff - Anmerkung zur Bearbeitungshistorie (en)" id="26"/>
-    <tableColumn name="Begriff - Verfasser des Eintrags" id="27"/>
-    <tableColumn name="Begriff - Kontextsatz (de)" id="28"/>
-    <tableColumn name="Begriff - Kontextsatz (en)" id="29"/>
-    <tableColumn name="Begriff - Bearbeitungsstatus" id="30"/>
-    <tableColumn name="Begriff - Mathematisches Symbol" id="31"/>
-    <tableColumn name="Begriff - Begriffsbeziehung - Oberbegriff" id="32"/>
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Verfasser - ID"/>
+    <tableColumn id="3" name="Verfasser  - Nachname"/>
+    <tableColumn id="4" name="Verfasser - Vorname"/>
+    <tableColumn id="5" name="Verfasser - ORCiD"/>
+    <tableColumn id="6" name="Quellennachweis - ID"/>
+    <tableColumn id="7" name="Quellennachweis - Titel"/>
+    <tableColumn id="8" name="Quellennachweis - Verfasser"/>
+    <tableColumn id="9" name="Quellennachweis - Herausgeber"/>
+    <tableColumn id="10" name="Quellennachweis - Erscheinungsdatum"/>
+    <tableColumn id="11" name="Quellennachweis - Zugangslink"/>
+    <tableColumn id="12" name="Begriff - ID"/>
+    <tableColumn id="13" name="Begriff - bevorzugte Benennung (de)"/>
+    <tableColumn id="14" name="Begriff - bevorzugte Benennung (en)"/>
+    <tableColumn id="15" name="Begriff - alternative Benennung (de)"/>
+    <tableColumn id="16" name="Begriff - alternative Benennung (en)"/>
+    <tableColumn id="17" name="Begriff - Definition (de)"/>
+    <tableColumn id="18" name="Begriff - Definition (en)"/>
+    <tableColumn id="19" name="Begriff - Quellenangabe"/>
+    <tableColumn id="20" name="Begriff - Bearbeitungsdatum"/>
+    <tableColumn id="21" name="Begriff - Fachzuordnung"/>
+    <tableColumn id="22" name="Begriff - Erstellungsdatum"/>
+    <tableColumn id="23" name="Begriff - redaktionelle Anmerkung (de)"/>
+    <tableColumn id="24" name="Begriff - redaktionelle Anmerkung (en)"/>
+    <tableColumn id="25" name="Begriff - Änderungsvermerk (de)"/>
+    <tableColumn id="26" name="Begriff - Anmerkung zur Änderungsvermerk (en)"/>
+    <tableColumn id="27" name="Begriff - Verfasser des Eintrags"/>
+    <tableColumn id="28" name="Begriff - Kontextsatz (de)"/>
+    <tableColumn id="29" name="Begriff - Kontextsatz (en)"/>
+    <tableColumn id="30" name="Begriff - Bearbeitungsstatus"/>
+    <tableColumn id="31" name="Begriff - Symbol oder Formelzeichen"/>
+    <tableColumn id="32" name="Begriff - Begriffsbeziehung - Oberbegriff"/>
   </tableColumns>
-  <tableStyleInfo name="Tabellenblatt1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Tabellenblatt1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -549,171 +581,174 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:AF2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="15.5"/>
-    <col customWidth="1" min="3" max="3" width="22.5"/>
-    <col customWidth="1" min="4" max="4" width="20.75"/>
-    <col customWidth="1" min="5" max="5" width="31.38"/>
-    <col customWidth="1" min="6" max="6" width="21.0"/>
-    <col customWidth="1" min="7" max="7" width="32.38"/>
-    <col customWidth="1" min="8" max="8" width="26.63"/>
-    <col customWidth="1" min="9" max="9" width="29.0"/>
-    <col customWidth="1" min="10" max="10" width="37.5"/>
-    <col customWidth="1" min="11" max="11" width="28.5"/>
-    <col customWidth="1" min="12" max="12" width="13.38"/>
-    <col customWidth="1" min="13" max="14" width="32.25"/>
-    <col customWidth="1" min="15" max="16" width="31.75"/>
-    <col customWidth="1" min="17" max="18" width="22.25"/>
-    <col customWidth="1" min="19" max="19" width="22.88"/>
-    <col customWidth="1" min="20" max="20" width="29.63"/>
-    <col customWidth="1" min="21" max="21" width="30.88"/>
-    <col customWidth="1" min="22" max="22" width="28.13"/>
-    <col customWidth="1" min="23" max="24" width="33.75"/>
-    <col customWidth="1" min="25" max="25" width="42.25"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" customWidth="1"/>
+    <col min="5" max="5" width="31.42578125" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="32.42578125" customWidth="1"/>
+    <col min="8" max="8" width="26.5703125" customWidth="1"/>
+    <col min="9" max="9" width="29" customWidth="1"/>
+    <col min="10" max="10" width="37.42578125" customWidth="1"/>
+    <col min="11" max="11" width="28.42578125" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+    <col min="13" max="14" width="32.28515625" customWidth="1"/>
+    <col min="15" max="16" width="31.7109375" customWidth="1"/>
+    <col min="17" max="18" width="22.28515625" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="29.5703125" customWidth="1"/>
+    <col min="21" max="21" width="30.85546875" customWidth="1"/>
+    <col min="22" max="22" width="28.140625" customWidth="1"/>
+    <col min="23" max="24" width="33.7109375" customWidth="1"/>
+    <col min="25" max="25" width="42.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AB1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AC1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AD1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AE1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>31</v>
-      </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8"/>
-      <c r="AB2" s="8"/>
-      <c r="AC2" s="8"/>
-      <c r="AD2" s="8"/>
-      <c r="AE2" s="8"/>
-      <c r="AF2" s="10"/>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="6"/>
     </row>
   </sheetData>
-  <dataValidations>
+  <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="T2 V2">
       <formula1>OR(NOT(ISERROR(DATEVALUE(T2))), AND(ISNUMBER(T2), LEFT(CELL("format", T2))="D"))</formula1>
     </dataValidation>
@@ -721,9 +756,10 @@
       <formula1>"Author,Source,Concept"</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/OpenRefine_Templates/OpenRefineTemplate_Blank.xlsx
+++ b/OpenRefine_Templates/OpenRefineTemplate_Blank.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Type</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>Begriff - Änderungsvermerk (de)</t>
+  </si>
+  <si>
+    <t>Begriff - ist Top Concept</t>
   </si>
 </sst>
 </file>
@@ -154,12 +157,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -172,9 +190,7 @@
       <top style="thin">
         <color rgb="FF284E3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -187,9 +203,7 @@
       <top style="thin">
         <color rgb="FF284E3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -202,97 +216,771 @@
       <top style="thin">
         <color rgb="FF284E3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF284E3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF284E3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF284E3F"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="37">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -334,9 +1022,9 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Tabellenblatt1-style" pivot="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="headerRow" dxfId="36"/>
+      <tableStyleElement type="firstRowStripe" dxfId="35"/>
+      <tableStyleElement type="secondRowStripe" dxfId="34"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -351,40 +1039,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:AF2" headerRowDxfId="0">
-  <tableColumns count="32">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Verfasser - ID"/>
-    <tableColumn id="3" name="Verfasser  - Nachname"/>
-    <tableColumn id="4" name="Verfasser - Vorname"/>
-    <tableColumn id="5" name="Verfasser - ORCiD"/>
-    <tableColumn id="6" name="Quellennachweis - ID"/>
-    <tableColumn id="7" name="Quellennachweis - Titel"/>
-    <tableColumn id="8" name="Quellennachweis - Verfasser"/>
-    <tableColumn id="9" name="Quellennachweis - Herausgeber"/>
-    <tableColumn id="10" name="Quellennachweis - Erscheinungsdatum"/>
-    <tableColumn id="11" name="Quellennachweis - Zugangslink"/>
-    <tableColumn id="12" name="Begriff - ID"/>
-    <tableColumn id="13" name="Begriff - bevorzugte Benennung (de)"/>
-    <tableColumn id="14" name="Begriff - bevorzugte Benennung (en)"/>
-    <tableColumn id="15" name="Begriff - alternative Benennung (de)"/>
-    <tableColumn id="16" name="Begriff - alternative Benennung (en)"/>
-    <tableColumn id="17" name="Begriff - Definition (de)"/>
-    <tableColumn id="18" name="Begriff - Definition (en)"/>
-    <tableColumn id="19" name="Begriff - Quellenangabe"/>
-    <tableColumn id="20" name="Begriff - Bearbeitungsdatum"/>
-    <tableColumn id="21" name="Begriff - Fachzuordnung"/>
-    <tableColumn id="22" name="Begriff - Erstellungsdatum"/>
-    <tableColumn id="23" name="Begriff - redaktionelle Anmerkung (de)"/>
-    <tableColumn id="24" name="Begriff - redaktionelle Anmerkung (en)"/>
-    <tableColumn id="25" name="Begriff - Änderungsvermerk (de)"/>
-    <tableColumn id="26" name="Begriff - Anmerkung zur Änderungsvermerk (en)"/>
-    <tableColumn id="27" name="Begriff - Verfasser des Eintrags"/>
-    <tableColumn id="28" name="Begriff - Kontextsatz (de)"/>
-    <tableColumn id="29" name="Begriff - Kontextsatz (en)"/>
-    <tableColumn id="30" name="Begriff - Bearbeitungsstatus"/>
-    <tableColumn id="31" name="Begriff - Symbol oder Formelzeichen"/>
-    <tableColumn id="32" name="Begriff - Begriffsbeziehung - Oberbegriff"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:AG2" insertRow="1" headerRowDxfId="33">
+  <tableColumns count="33">
+    <tableColumn id="1" name="Type" dataDxfId="32"/>
+    <tableColumn id="2" name="Verfasser - ID" dataDxfId="31"/>
+    <tableColumn id="3" name="Verfasser  - Nachname" dataDxfId="30"/>
+    <tableColumn id="4" name="Verfasser - Vorname" dataDxfId="29"/>
+    <tableColumn id="5" name="Verfasser - ORCiD" dataDxfId="28"/>
+    <tableColumn id="6" name="Quellennachweis - ID" dataDxfId="27"/>
+    <tableColumn id="7" name="Quellennachweis - Titel" dataDxfId="26"/>
+    <tableColumn id="8" name="Quellennachweis - Verfasser" dataDxfId="25"/>
+    <tableColumn id="9" name="Quellennachweis - Herausgeber" dataDxfId="24"/>
+    <tableColumn id="10" name="Quellennachweis - Erscheinungsdatum" dataDxfId="23"/>
+    <tableColumn id="11" name="Quellennachweis - Zugangslink" dataDxfId="22"/>
+    <tableColumn id="12" name="Begriff - ID" dataDxfId="21"/>
+    <tableColumn id="13" name="Begriff - bevorzugte Benennung (de)" dataDxfId="20"/>
+    <tableColumn id="14" name="Begriff - bevorzugte Benennung (en)" dataDxfId="19"/>
+    <tableColumn id="15" name="Begriff - alternative Benennung (de)" dataDxfId="18"/>
+    <tableColumn id="16" name="Begriff - alternative Benennung (en)" dataDxfId="17"/>
+    <tableColumn id="17" name="Begriff - Definition (de)" dataDxfId="16"/>
+    <tableColumn id="18" name="Begriff - Definition (en)" dataDxfId="15"/>
+    <tableColumn id="19" name="Begriff - Quellenangabe" dataDxfId="14"/>
+    <tableColumn id="20" name="Begriff - Bearbeitungsdatum" dataDxfId="13"/>
+    <tableColumn id="21" name="Begriff - Fachzuordnung" dataDxfId="12"/>
+    <tableColumn id="22" name="Begriff - Erstellungsdatum" dataDxfId="11"/>
+    <tableColumn id="23" name="Begriff - redaktionelle Anmerkung (de)" dataDxfId="10"/>
+    <tableColumn id="24" name="Begriff - redaktionelle Anmerkung (en)" dataDxfId="9"/>
+    <tableColumn id="25" name="Begriff - Änderungsvermerk (de)" dataDxfId="8"/>
+    <tableColumn id="26" name="Begriff - Anmerkung zur Änderungsvermerk (en)" dataDxfId="7"/>
+    <tableColumn id="27" name="Begriff - Verfasser des Eintrags" dataDxfId="6"/>
+    <tableColumn id="28" name="Begriff - Kontextsatz (de)" dataDxfId="5"/>
+    <tableColumn id="29" name="Begriff - Kontextsatz (en)" dataDxfId="4"/>
+    <tableColumn id="30" name="Begriff - Bearbeitungsstatus" dataDxfId="3"/>
+    <tableColumn id="31" name="Begriff - Symbol oder Formelzeichen" dataDxfId="2"/>
+    <tableColumn id="32" name="Begriff - Begriffsbeziehung - Oberbegriff" dataDxfId="1"/>
+    <tableColumn id="33" name="Begriff - ist Top Concept" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Tabellenblatt1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -591,7 +1280,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
@@ -616,136 +1305,141 @@
     <col min="25" max="25" width="42.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="W1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="8" t="s">
+      <c r="X1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Y1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="Z1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AA1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AB1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="8" t="s">
+      <c r="AC1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="8" t="s">
+      <c r="AD1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="8" t="s">
+      <c r="AE1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="10" t="s">
+      <c r="AF1" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="4"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="A2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
       <c r="AF2" s="6"/>
+      <c r="AG2" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/OpenRefine_Templates/OpenRefineTemplate_Blank.xlsx
+++ b/OpenRefine_Templates/OpenRefineTemplate_Blank.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>Type</t>
   </si>
@@ -118,6 +118,18 @@
   </si>
   <si>
     <t>Begriff - ist Top Concept</t>
+  </si>
+  <si>
+    <t>Begriff - ist veraltet?</t>
+  </si>
+  <si>
+    <t>Begriff - hat Nachfolger</t>
+  </si>
+  <si>
+    <t>Begriff - Grund der Markierung als veraltet (de)</t>
+  </si>
+  <si>
+    <t>Begriff - Grund der Markierung als veraltet (en)</t>
   </si>
 </sst>
 </file>
@@ -223,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -250,11 +262,88 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="41">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1022,9 +1111,9 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Tabellenblatt1-style" pivot="0" count="3">
-      <tableStyleElement type="headerRow" dxfId="36"/>
-      <tableStyleElement type="firstRowStripe" dxfId="35"/>
-      <tableStyleElement type="secondRowStripe" dxfId="34"/>
+      <tableStyleElement type="headerRow" dxfId="40"/>
+      <tableStyleElement type="firstRowStripe" dxfId="39"/>
+      <tableStyleElement type="secondRowStripe" dxfId="38"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1039,41 +1128,45 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:AG2" insertRow="1" headerRowDxfId="33">
-  <tableColumns count="33">
-    <tableColumn id="1" name="Type" dataDxfId="32"/>
-    <tableColumn id="2" name="Verfasser - ID" dataDxfId="31"/>
-    <tableColumn id="3" name="Verfasser  - Nachname" dataDxfId="30"/>
-    <tableColumn id="4" name="Verfasser - Vorname" dataDxfId="29"/>
-    <tableColumn id="5" name="Verfasser - ORCiD" dataDxfId="28"/>
-    <tableColumn id="6" name="Quellennachweis - ID" dataDxfId="27"/>
-    <tableColumn id="7" name="Quellennachweis - Titel" dataDxfId="26"/>
-    <tableColumn id="8" name="Quellennachweis - Verfasser" dataDxfId="25"/>
-    <tableColumn id="9" name="Quellennachweis - Herausgeber" dataDxfId="24"/>
-    <tableColumn id="10" name="Quellennachweis - Erscheinungsdatum" dataDxfId="23"/>
-    <tableColumn id="11" name="Quellennachweis - Zugangslink" dataDxfId="22"/>
-    <tableColumn id="12" name="Begriff - ID" dataDxfId="21"/>
-    <tableColumn id="13" name="Begriff - bevorzugte Benennung (de)" dataDxfId="20"/>
-    <tableColumn id="14" name="Begriff - bevorzugte Benennung (en)" dataDxfId="19"/>
-    <tableColumn id="15" name="Begriff - alternative Benennung (de)" dataDxfId="18"/>
-    <tableColumn id="16" name="Begriff - alternative Benennung (en)" dataDxfId="17"/>
-    <tableColumn id="17" name="Begriff - Definition (de)" dataDxfId="16"/>
-    <tableColumn id="18" name="Begriff - Definition (en)" dataDxfId="15"/>
-    <tableColumn id="19" name="Begriff - Quellenangabe" dataDxfId="14"/>
-    <tableColumn id="20" name="Begriff - Bearbeitungsdatum" dataDxfId="13"/>
-    <tableColumn id="21" name="Begriff - Fachzuordnung" dataDxfId="12"/>
-    <tableColumn id="22" name="Begriff - Erstellungsdatum" dataDxfId="11"/>
-    <tableColumn id="23" name="Begriff - redaktionelle Anmerkung (de)" dataDxfId="10"/>
-    <tableColumn id="24" name="Begriff - redaktionelle Anmerkung (en)" dataDxfId="9"/>
-    <tableColumn id="25" name="Begriff - Änderungsvermerk (de)" dataDxfId="8"/>
-    <tableColumn id="26" name="Begriff - Anmerkung zur Änderungsvermerk (en)" dataDxfId="7"/>
-    <tableColumn id="27" name="Begriff - Verfasser des Eintrags" dataDxfId="6"/>
-    <tableColumn id="28" name="Begriff - Kontextsatz (de)" dataDxfId="5"/>
-    <tableColumn id="29" name="Begriff - Kontextsatz (en)" dataDxfId="4"/>
-    <tableColumn id="30" name="Begriff - Bearbeitungsstatus" dataDxfId="3"/>
-    <tableColumn id="31" name="Begriff - Symbol oder Formelzeichen" dataDxfId="2"/>
-    <tableColumn id="32" name="Begriff - Begriffsbeziehung - Oberbegriff" dataDxfId="1"/>
-    <tableColumn id="33" name="Begriff - ist Top Concept" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabelle1" displayName="Tabelle1" ref="A1:AK2" insertRow="1" headerRowDxfId="37">
+  <tableColumns count="37">
+    <tableColumn id="1" name="Type" dataDxfId="36"/>
+    <tableColumn id="2" name="Verfasser - ID" dataDxfId="35"/>
+    <tableColumn id="3" name="Verfasser  - Nachname" dataDxfId="34"/>
+    <tableColumn id="4" name="Verfasser - Vorname" dataDxfId="33"/>
+    <tableColumn id="5" name="Verfasser - ORCiD" dataDxfId="32"/>
+    <tableColumn id="6" name="Quellennachweis - ID" dataDxfId="31"/>
+    <tableColumn id="7" name="Quellennachweis - Titel" dataDxfId="30"/>
+    <tableColumn id="8" name="Quellennachweis - Verfasser" dataDxfId="29"/>
+    <tableColumn id="9" name="Quellennachweis - Herausgeber" dataDxfId="28"/>
+    <tableColumn id="10" name="Quellennachweis - Erscheinungsdatum" dataDxfId="27"/>
+    <tableColumn id="11" name="Quellennachweis - Zugangslink" dataDxfId="26"/>
+    <tableColumn id="12" name="Begriff - ID" dataDxfId="25"/>
+    <tableColumn id="13" name="Begriff - bevorzugte Benennung (de)" dataDxfId="24"/>
+    <tableColumn id="14" name="Begriff - bevorzugte Benennung (en)" dataDxfId="23"/>
+    <tableColumn id="15" name="Begriff - alternative Benennung (de)" dataDxfId="22"/>
+    <tableColumn id="16" name="Begriff - alternative Benennung (en)" dataDxfId="21"/>
+    <tableColumn id="17" name="Begriff - Definition (de)" dataDxfId="20"/>
+    <tableColumn id="18" name="Begriff - Definition (en)" dataDxfId="19"/>
+    <tableColumn id="19" name="Begriff - Quellenangabe" dataDxfId="18"/>
+    <tableColumn id="20" name="Begriff - Bearbeitungsdatum" dataDxfId="17"/>
+    <tableColumn id="21" name="Begriff - Fachzuordnung" dataDxfId="16"/>
+    <tableColumn id="22" name="Begriff - Erstellungsdatum" dataDxfId="15"/>
+    <tableColumn id="23" name="Begriff - redaktionelle Anmerkung (de)" dataDxfId="14"/>
+    <tableColumn id="24" name="Begriff - redaktionelle Anmerkung (en)" dataDxfId="13"/>
+    <tableColumn id="25" name="Begriff - Änderungsvermerk (de)" dataDxfId="12"/>
+    <tableColumn id="26" name="Begriff - Anmerkung zur Änderungsvermerk (en)" dataDxfId="11"/>
+    <tableColumn id="27" name="Begriff - Verfasser des Eintrags" dataDxfId="10"/>
+    <tableColumn id="28" name="Begriff - Kontextsatz (de)" dataDxfId="9"/>
+    <tableColumn id="29" name="Begriff - Kontextsatz (en)" dataDxfId="8"/>
+    <tableColumn id="30" name="Begriff - Bearbeitungsstatus" dataDxfId="7"/>
+    <tableColumn id="31" name="Begriff - Symbol oder Formelzeichen" dataDxfId="6"/>
+    <tableColumn id="32" name="Begriff - Begriffsbeziehung - Oberbegriff" dataDxfId="5"/>
+    <tableColumn id="33" name="Begriff - ist Top Concept" dataDxfId="4"/>
+    <tableColumn id="34" name="Begriff - ist veraltet?" dataDxfId="3"/>
+    <tableColumn id="35" name="Begriff - hat Nachfolger" dataDxfId="2"/>
+    <tableColumn id="36" name="Begriff - Grund der Markierung als veraltet (de)" dataDxfId="1"/>
+    <tableColumn id="37" name="Begriff - Grund der Markierung als veraltet (en)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Tabellenblatt1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1280,7 +1373,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
@@ -1305,7 +1398,7 @@
     <col min="25" max="25" width="42.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1405,8 +1498,20 @@
       <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="AH1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="10" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
       <c r="C2" s="6"/>
@@ -1440,6 +1545,10 @@
       <c r="AE2" s="6"/>
       <c r="AF2" s="6"/>
       <c r="AG2" s="8"/>
+      <c r="AH2" s="8"/>
+      <c r="AI2" s="8"/>
+      <c r="AJ2" s="8"/>
+      <c r="AK2" s="8"/>
     </row>
   </sheetData>
   <dataValidations count="2">
